--- a/output/final/dc/dc distributors (status checked)/flagged_for_review.xlsx
+++ b/output/final/dc/dc distributors (status checked)/flagged_for_review.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flagged for review" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Flagged for review'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Flagged for review'!$A$1:$F$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,7 +51,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -119,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -131,12 +126,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -505,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -580,43 +569,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="33" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Global Data Center Market</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Drive Control Corporation Pty Ltd (acquired by DCC Technologies)</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>drivecon.net</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Johannesburg, South Africa</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>absorbed (acquired by Kleoss Capital and private investor group)</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Two different owners found: 'DCC Technologies' (earlier check) vs 'Kleoss Capital' (status check).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F3"/>
+  <autoFilter ref="A1:F2"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
